--- a/reports/daily_report_2026-06-14.xlsx
+++ b/reports/daily_report_2026-06-14.xlsx
@@ -349,12 +349,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="7200000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>83.33</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="7">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -754,7 +754,17 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>超时申请数</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -771,14 +781,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -807,34 +822,74 @@
           <t>待审批</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>通过率(%)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>同步成功数</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>同步成功率(%)</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>平均时长(h)</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>超时数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>测试部门</t>
+          <t>销售一部</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>VIP部门</t>
+          <t>销售二部</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
@@ -843,6 +898,21 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,7 +923,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
@@ -862,7 +932,22 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -877,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -903,13 +988,13 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>CONTACT_INFO</t>
+          <t>BATCH_TEST_0</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -919,7 +1004,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>PHONE_CHANGE</t>
+          <t>BATCH_TEST_1</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -929,7 +1014,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>RISK_TEST_0</t>
+          <t>BATCH_TEST_2</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -939,7 +1024,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>RISK_TEST_1</t>
+          <t>RISK_TEST_0</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -949,10 +1034,30 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>RISK_TEST_1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>RISK_TEST_2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>RISK_TRIGGER</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
     </row>
